--- a/Теория кодирования, сжатия и восст инф/Лабы/ЛР 1.xlsx
+++ b/Теория кодирования, сжатия и восст инф/Лабы/ЛР 1.xlsx
@@ -1,42 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Теория кодирования, сжатия и восст инф\Лабы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrcov\Desktop\Fourth_course\Теория кодирования, сжатия и восст инф\Лабы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337254C2-84A0-4322-A0ED-25B28C427D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1108D57C-9972-4C61-8662-499D67DCD9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{494DAEA0-D604-48B6-BE09-702306B90502}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="1" xr2:uid="{494DAEA0-D604-48B6-BE09-702306B90502}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Шеннона-Фано" sheetId="1" r:id="rId1"/>
+    <sheet name="Хаффмана" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="57">
   <si>
     <t>S1</t>
   </si>
@@ -120,13 +113,100 @@
   </si>
   <si>
     <t>11111</t>
+  </si>
+  <si>
+    <t>Вар. 7</t>
+  </si>
+  <si>
+    <t>0,02 (1)</t>
+  </si>
+  <si>
+    <t>0,01 (0)</t>
+  </si>
+  <si>
+    <t>0,03 (0)</t>
+  </si>
+  <si>
+    <t>0,04 (1)</t>
+  </si>
+  <si>
+    <t>0,06 (1)</t>
+  </si>
+  <si>
+    <t>0,05 (0)</t>
+  </si>
+  <si>
+    <t>0,08 (1)</t>
+  </si>
+  <si>
+    <t>0,07 (0)</t>
+  </si>
+  <si>
+    <t>0,11 (1)</t>
+  </si>
+  <si>
+    <t>0,09 (0)</t>
+  </si>
+  <si>
+    <t>0,14 (1)</t>
+  </si>
+  <si>
+    <t>0,13 (0)</t>
+  </si>
+  <si>
+    <t>0,11 (0)</t>
+  </si>
+  <si>
+    <t>0,12 (1)</t>
+  </si>
+  <si>
+    <t>0,15 (1)</t>
+  </si>
+  <si>
+    <t>0,15 (0)</t>
+  </si>
+  <si>
+    <t>0,23 (1)</t>
+  </si>
+  <si>
+    <t>0,2 (0)</t>
+  </si>
+  <si>
+    <t>0,3 (1)</t>
+  </si>
+  <si>
+    <t>0,27 (0)</t>
+  </si>
+  <si>
+    <t>0,57 (1)</t>
+  </si>
+  <si>
+    <t>0,43 (0)</t>
+  </si>
+  <si>
+    <t>Вспомогательные столбцы</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>001001</t>
+  </si>
+  <si>
+    <t>001000</t>
+  </si>
+  <si>
+    <t>00101</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,7 +239,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -219,15 +299,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -235,10 +377,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -249,13 +397,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -273,6 +457,125 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>366395</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>52070</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{256B67C2-B60A-45E8-8E9D-745DD3E90A78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="14407" r="18701" b="22120"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4105275" y="5057775"/>
+          <a:ext cx="6005195" cy="2442845"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+            <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>62230</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B6F2622-8DC4-4884-97F7-B34F0DDE8776}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4143375" y="4686300"/>
+          <a:ext cx="5940425" cy="3519805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,443 +895,551 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E28668B-FA39-45D5-9930-5D47C66ED0E8}">
-  <dimension ref="C3:O23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:O40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C3" s="1">
+    <row r="3" spans="3:15">
+      <c r="C3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="L3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="3:15">
+      <c r="C4" s="14"/>
+      <c r="D4" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6" spans="3:15">
+      <c r="C6" s="10">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="7" spans="3:15">
+      <c r="C7" s="10"/>
+      <c r="D7" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15">
+      <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" ht="30.75" customHeight="1">
+      <c r="C11" s="6"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F11" s="1">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H11" s="1">
         <v>4</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I11" s="1">
         <v>5</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="3:15">
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15">
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="D13" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="7">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15">
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15">
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="7">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15">
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="7">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10">
+      <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="D19" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="12">
+        <v>1</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
+      <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="D20" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10">
+        <v>1</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10">
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10">
+      <c r="C23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="3">
+        <v>1</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10">
+      <c r="C27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10">
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="3:10">
+      <c r="C29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10">
+      <c r="C30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10">
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10">
+      <c r="C32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="D35" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="1"/>
-      <c r="D4" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="1">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="D38" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="D39" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4">
+      <c r="C40" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="1"/>
-      <c r="D7" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="N7" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="O7" s="2">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2">
-        <v>4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>5</v>
-      </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="6">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="6">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="6">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="9">
-        <v>1</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="5">
-        <v>1</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="5">
-        <v>1</v>
-      </c>
-      <c r="J23" s="11" t="s">
+      <c r="D40" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1036,23 +1447,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:O4">
     <sortCondition descending="1" ref="D3:D4"/>
   </sortState>
-  <mergeCells count="24">
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="G20:G23"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
+  <mergeCells count="26">
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="E12:E15"/>
@@ -1061,11 +1458,919 @@
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="F16:F17"/>
     <mergeCell ref="F18:F23"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="G20:G23"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="G15:I15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="J12:J23" numberStoredAsText="1"/>
+    <ignoredError sqref="J12:J23 D29:D40" numberStoredAsText="1"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8D0337-401A-444A-A835-D737C3857AB9}">
+  <dimension ref="C3:Q40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="11.125" customWidth="1"/>
+    <col min="5" max="14" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:17">
+      <c r="C3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="3:17">
+      <c r="C4" s="14"/>
+      <c r="D4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17">
+      <c r="C6" s="10">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17">
+      <c r="C7" s="10"/>
+      <c r="D7" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="O7" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17">
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="3:17">
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="19">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19">
+        <v>2</v>
+      </c>
+      <c r="G12" s="19">
+        <v>3</v>
+      </c>
+      <c r="H12" s="19">
+        <v>4</v>
+      </c>
+      <c r="I12" s="19">
+        <v>5</v>
+      </c>
+      <c r="J12" s="19">
+        <v>6</v>
+      </c>
+      <c r="K12" s="19">
+        <v>7</v>
+      </c>
+      <c r="L12" s="19">
+        <v>8</v>
+      </c>
+      <c r="M12" s="19">
+        <v>9</v>
+      </c>
+      <c r="N12" s="19">
+        <v>10</v>
+      </c>
+      <c r="O12" s="19">
+        <v>11</v>
+      </c>
+      <c r="P12" s="22"/>
+    </row>
+    <row r="13" spans="3:17">
+      <c r="C13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="I13" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0.23</v>
+      </c>
+      <c r="K13" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="L13" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0.43</v>
+      </c>
+      <c r="N13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" s="20">
+        <v>1</v>
+      </c>
+      <c r="P13" s="23">
+        <v>111</v>
+      </c>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" spans="3:17">
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O14" s="19"/>
+      <c r="P14" s="23">
+        <v>101</v>
+      </c>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" spans="3:17">
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="3:17">
+      <c r="C16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="3:17">
+      <c r="C17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q17" s="24"/>
+    </row>
+    <row r="18" spans="3:17">
+      <c r="C18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="24"/>
+    </row>
+    <row r="19" spans="3:17">
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="3:17">
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F20" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17">
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17">
+      <c r="C22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17">
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17">
+      <c r="C24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17">
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+    </row>
+    <row r="26" spans="3:17">
+      <c r="C26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+    </row>
+    <row r="27" spans="3:17">
+      <c r="C27" s="6"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+    </row>
+    <row r="28" spans="3:17">
+      <c r="C28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="23">
+        <v>111</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+    </row>
+    <row r="29" spans="3:17">
+      <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="23">
+        <v>101</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="3:17">
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="23">
+        <v>100</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="3:17">
+      <c r="C31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="3:17">
+      <c r="C32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="3:15">
+      <c r="C33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="3:15">
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="3:15">
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="3:15">
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="3:15">
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="3:15">
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="3:15">
+      <c r="C39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="3:15">
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E11:O11"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="P16:P24 D31:D39" numberStoredAsText="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>